--- a/historico_c5/tarjetas_informativas/CONCENTRADO_MASTER_TARJETAS_INFORMATIVAS.xlsx
+++ b/historico_c5/tarjetas_informativas/CONCENTRADO_MASTER_TARJETAS_INFORMATIVAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,51 @@
           <t>id_tarjeta</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>victima</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>edad</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>casquillos</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>policia_unidad</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>imagen_path</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>folio_911_vinculado</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>incidente_911</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>coincidencia_estatus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +532,153 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>TI-20260728_133304</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ECATEPEC (PERSONA MUERTA POR IMPACTOS DE BALA)
+A las 10:55 horas, el Policía GUTIERREZ RAMIREZ JUAN CARLOS unidad ME334A, informó que, en calle Colorines esquina calle Encino, colonia Tierra Blanca, hizo contacto con el Primer Respondiente Policía Municipal FERMÍN GUZMÁN FERNANDO unidad sector 3-21, indicando de una persona muerta por impactos de bala, quien respondía al nombre de RICARDO HERNÁNDEZ MAYA REYNOSA de 33 años, localizándose en el lugar 5 casquillos percutidos de calibre 9mm; arribo personal de Protección Civil unidad PC-2021, al mando del Paramédico JUAN CARLOS GALVÁN, quien certifica que ya no cuentan con signos vitales.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:36:18</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RICARDO HERNÁNDEZ MAYA REYNOSA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5 casquillos calibre 9m</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GUTIERREZ RAMIREZ JUAN CARLOS (ME334A)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>calle Colorines esquina calle Encino, colonia Tierra Blanca</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>whatsapp_ecatepec_colorines.png</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ECA26072301237</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ACCIDENTE DE TRANSITO SIN PERSONAS LESIONADAS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TECÁMAC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TECÁMAC (PERSONA MUERTA POR IMPACTO DE BALA)
+A las 23:55 horas, el Policía MALDONADO SUÁREZ JUAN TRINIDAD, unidad ME937A5, informó que a las 06:15 horas, en calle Jardines de La Viña esquina 2da. Cerrada de Jardines de La Viña, fraccionamiento Héroes Tecámac, hizo contacto con la Primer Respondiente Policía Municipal NORMA HERNÁNDEZ CASTRO unidad C-072, quien toma conocimiento de una persona muerta quien en vida respondía al nombre de LUIS EDUARDO RUIZ ROJAS de 35 años, el cual se encuentra a bordo de un vehículo marca Chevrolet, tipo Chevy Monza, color blanco, placas PUB383E, con bandera de taxi, localizando 7 casquillos percutidos calibre 9mm, arribo la Unidad Médica PC-70, al mando de la Paramédico ROCIÓ ZARATE RANGEL, indicando que ya no cuenta con signos vitales, debido a los impactos que presenta en la cara, indica la Primer Respondiente que se trató de un intento de asalto y al oponer resistencia le disparan.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:36:26</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO RUIZ ROJAS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7 casquillos 9mm</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Municipal NORMA HERNÁNDEZ CASTRO (C-072)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No especificada</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>whatsapp_tecamac_chevy.png</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SIN REGISTRO PREVIO 911</t>
         </is>
       </c>
     </row>

--- a/historico_c5/tarjetas_informativas/CONCENTRADO_MASTER_TARJETAS_INFORMATIVAS.xlsx
+++ b/historico_c5/tarjetas_informativas/CONCENTRADO_MASTER_TARJETAS_INFORMATIVAS.xlsx
@@ -413,272 +413,4133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>origen</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>victima</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>edad</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>casquillos</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>policia_unidad</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>hora</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delito</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>narrativa_completa</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>acciones_ssem</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>folio_911_vinculado</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>coincidencia_estatus</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>id_tarjeta</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>fecha_registro</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id_tarjeta</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>victima</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>edad</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>casquillos</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>policia_unidad</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ubicacion</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>imagen_path</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>folio_911_vinculado</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>incidente_911</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>coincidencia_estatus</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>EXCEL_CORROBORADOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:30 hrs</t>
+          <t>HUEHUETOCA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ECATEPEC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>INCIDENTE RELEVANTE</t>
-        </is>
-      </c>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TARJETA INFORMATIVA - 28/07/2026. En Ecatepec a las 11:30 hrs se reportó detonaciones de arma de fuego en colonia Centro.</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-28 13:33:04</t>
+          <t>SSEM DGSPYT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TI-20260728_133304</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>C PASEO DE SAN ANTONIO, Col. CIUDAD SANTA TERESA VII</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>04:12:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Jonathan Yair Estrada Nava (26) fue localizado sin vida con impactos de arma de fuego, al interior de un domicilio</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>* se realiza el acordonamiento del lugar de los hechos en coordinacion y apoyo a la policia municipal (primer respondiente).
+* se establece un perimetro de seguridad.
+• En el sitio no se localizan cámaras de video vigilancia.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ECA26072401063</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-001</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>NEXTLALPAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ECATEPEC</t>
+          <t>DESCONOCIDO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ECATEPEC (PERSONA MUERTA POR IMPACTOS DE BALA)
-A las 10:55 horas, el Policía GUTIERREZ RAMIREZ JUAN CARLOS unidad ME334A, informó que, en calle Colorines esquina calle Encino, colonia Tierra Blanca, hizo contacto con el Primer Respondiente Policía Municipal FERMÍN GUZMÁN FERNANDO unidad sector 3-21, indicando de una persona muerta por impactos de bala, quien respondía al nombre de RICARDO HERNÁNDEZ MAYA REYNOSA de 33 años, localizándose en el lugar 5 casquillos percutidos de calibre 9mm; arribo personal de Protección Civil unidad PC-2021, al mando del Paramédico JUAN CARLOS GALVÁN, quien certifica que ya no cuentan con signos vitales.</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-28 13:36:18</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C FRESNOS ESQUINA NOGALES, Col. PRADOS DE SAN FRANCISCO</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RICARDO HERNÁNDEZ MAYA REYNOSA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>33</v>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Hemir Ezequiel Gonzalez Alemán (22) perdió la vida por disparos de arma de fuego en la extremidad cefálica, en el patio del domicilio.</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5 casquillos calibre 9m</t>
+          <t>En pláticas con vecinos refieren que dicha persona no es de la zona  que llego a vivir solo y que no cuenta con algún familiar cercano.
+• Así mismo comentan vecinos que se encontraba ingiriendo bebidas alcohólicas con más personas y solo escucharon que comenzaron a discutir y en seguida se escuchó un ruido al parecer de dos detonaciones.
+• Se hace un extenso recorrido sobre la zona intentando localizar alguna cámara de Videovigilancia (C-5) y/o particulares, encontrando una a escasos 50 metros, así como una del C-2 en la esquina de Fresnos y Nogales las cuáles se solicitarán.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GUTIERREZ RAMIREZ JUAN CARLOS (ME334A)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>calle Colorines esquina calle Encino, colonia Tierra Blanca</t>
+          <t>SIN REGISTRO PREVIO 911</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>whatsapp_ecatepec_colorines.png</t>
+          <t>TI-MASIVA-002</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ECA26072301237</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ACCIDENTE DE TRANSITO SIN PERSONAS LESIONADAS</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>VINCULADA 911 C5</t>
+          <t>2026-07-28 13:38:41</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>ACOLMAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TECÁMAC</t>
+          <t>DESCONOCIDO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TECÁMAC (PERSONA MUERTA POR IMPACTO DE BALA)
-A las 23:55 horas, el Policía MALDONADO SUÁREZ JUAN TRINIDAD, unidad ME937A5, informó que a las 06:15 horas, en calle Jardines de La Viña esquina 2da. Cerrada de Jardines de La Viña, fraccionamiento Héroes Tecámac, hizo contacto con la Primer Respondiente Policía Municipal NORMA HERNÁNDEZ CASTRO unidad C-072, quien toma conocimiento de una persona muerta quien en vida respondía al nombre de LUIS EDUARDO RUIZ ROJAS de 35 años, el cual se encuentra a bordo de un vehículo marca Chevrolet, tipo Chevy Monza, color blanco, placas PUB383E, con bandera de taxi, localizando 7 casquillos percutidos calibre 9mm, arribo la Unidad Médica PC-70, al mando de la Paramédico ROCIÓ ZARATE RANGEL, indicando que ya no cuenta con signos vitales, debido a los impactos que presenta en la cara, indica la Primer Respondiente que se trató de un intento de asalto y al oponer resistencia le disparan.</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-28 13:36:26</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C REAL DEL VALLE SUR ESQUINA VALLE DORADO, Col. LOS ÁNGELES</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>01:05:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>José Manuel Reynaga Chávez (18) perdió la vida por impactos de arma de fuego en diversas partes del cuerpo, en el lugar se localizaron cinco casquillos calibre 9mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>• Se apoya con el acordonamiento del lugar de los hechos.
+• Se establece un perímetro de seguridad en el lugar.
+• Se realiza inspección para ubicar cámaras de video vigilancia.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ECA26072302393</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-003</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CHALCO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C PERA ESQUINA BOULEVARD CUATRO VIENTOS, Col. SAN MARCOS HUIXTOCO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Un hombre de aproximadamente 45 años fue localizado sin vida con impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>* se realiza el acordonamiento del lugar de los hechos en coordinacion y apoyo a la policia municipal (primer respondiente).
+* se establece un perimetro de seguridad.
+• En el sitio no se localizan cámaras de video vigilancia.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ECA26072302921</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-004</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TULTITLAN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>C CEREZO ESQUINA VIOLETA, Col. AMPLIACIÓN SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>08:10:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fátima Marisol Trejo Vásquez (21) fue localizada sin vida con disparos de arma de fuego en el tórax.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Se realizan entrevista con familiares de la hoy occisa mencionando que la femenina venía a ese domicilio a recoger a su menor hijo de 5 años para llevarlo a la escuela, mencionando que su esposo de nombre Roberto Hernández Longinos de 25 años, está recluido en el penal de Tenango del Valle por homicidio calificado y la madre de la occisa de nombre Fátima Trejo Vázquez de 35 años se encuentra recluida en el penal de Barrientos por delitos contra la salud 
+Mediante investigaciones sobre la femenina sin signos vitales, en entrevista con la C. Ericka Hernández Lonjinos (cuñada de la occisa) manifiesta que tenía una disputa con la misma por la custodia de 02 hermanos y su menor hijo, mencionando también que la occisa trabajaba en un bar, de sexoservidora y vendía sustancias ilícitas, los peritos al momento de realizar la inspección encuentra en la mochila de la fallecida ropa provocativa siendo esta minifalda, tacones (sexoservidora).</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ECA26072504856</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-005</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>C PROLONGACIÓN MIGUEL HIDALGO ESQUINA AV BENITO JUÁREZ, Col. SAN PEDRO BARRIENTOS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>00:50:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Un hombre (30) y una mujer (25) perdieron la vida por impactos de arma de fuego en un vehículo Chevrolet Aveo, placas NBC299A, propiedad de Polo Trejo Sánchez (sin reporte de robo).</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Por las cámaras de C-4, indica que cruzan caminando 2 masculinos y directos se van hacia el carro ya que por comentarios de las personas indican que el vehículo se paró totalmente orillándose, como esperando a alguien posteriormente escucharon las detonaciones donde se ve que el ataque fue directo. Al visualizar la femenina ya en varias ocasiones, había sido inspeccionada por elementos de SSEM, en un punto de venta de droga, así como en una ocasión se acercó haciéndose pasar como familiar de dos menores del sexo femenino, quienes fueron detenidas y presentas en la fiscalía para adolescentes por el delito de delitos contra la salud. </t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ECA26072301614</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-006</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NEZAHUALCOYOTL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>C. 5 ESQUINA AV 2, Col. LAS AGUILAS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>22:40:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Omar Gálvez Velázquez (44) perdió la vida pro impactos de arma de fuego en el abdomen.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Vigilancia perimetral y recorridos para tratar de locailizar el vehiculo y  los responsables</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ECA26072302400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-007</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>C UNIÓN, Col. EJÉRCITO DEL TRABAJO II</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Un hombre (a) "El Monki" perdió la vida por impactos de arma de fuego en extremidad torácica, a bordo de un vehículo Volkswagen Vento, derivado de una riña entre dos hombres y una mujer.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>* Se entrevista con vecinos del lugar indicando que el vehículo vento color blanco lo habían reportado los vecinos en un grupo de WhatsApp (red vecinal) que se encontraba en lugar dando vueltas, refiriendo que no lo conocían, por lo que lo publicaron para solicitar la intervención de unidades oficiales.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ECA26072302471</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-008</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AXAPUSCO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>C PRIMAVERA ESQUINA BENITO JUÁREZ, Col. AXAPUSCO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>02:30:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Juan Carlos Salas Rojas (22) perdió la vida y Diego Aldair Hernández Delgadillo (19) y Felipe de Jesús Salas Castro, resultaron lesionados por impactos de arma de fuego, cuando viajaban a bordo de un vehículo; los heridos fueron trasladados al Hospital General de Axapusco.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Se implementan los Operativos Pistón, Pegaso, Construcción por la Paz, Intermunicipal, C.E.M., Transporte Estatal Seguro, con la finalidad de evitar y erradicar la incidencia de homicidios dolosos, en el Municipio de Axapusco.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ECA26072701155</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-009</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CALZADA SAN ESTEBAN NO. 136, Col. SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01:50:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Un hombre perdió la vida por impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>•Se hace la detención  por parte de la Policia Estatal de un  masculino de nombre Gerardo Flores Cruz de 43 años de edad, relacionado con el homicidio.
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Se tiene contacto con el empleado de la tienda con razón social 7ELEVEN, quien no proporciona generales, indicando que había observado al masculino parado en la puerta de su tienda cuando de pronto escuchó las detonaciones y observa que corre un aproximado de 15 metros y al asomarse ve al masculino en el suelo</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TOL26072402979</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-010</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA PAZ </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CALLE LIBERTAD ESQUINA CENTENARIO, Col. EMILIANO ZAPATA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01:05:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Eleazar González García (48) perdió la vcida por disparos de arma de fuego y José Armando González Herrada (24) resultó lesionado por la misma causa, el herido fue trasladado al Hospital La Perla en Nezahualcóyotl.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Se da seguimiento con la Dirección de Unidad de Inteligencia e Investigación para la Prevención y con la Fiscalia Especializada de Homicidios de Alto Impacto del estado de México para la detención de los responsables del homicidio.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SIN REGISTRO PREVIO 911</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-011</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NEZAHUALCOYOTL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>C SANTA MÓNICA, Col. AMPLIACIÓN VICENTE VILLADA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>03:10:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Cristofer Monroy Martínez (a) "corona" (43) perdió la vida por impacto de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Vigilancia perimetral y recorridos para tratar de locailizar el vehiculo y  los responsables</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ECA26072207727</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-012</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEZAHUALCOYOTL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LAGO MUSRTER, Col. C CIUDAD LAGO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Un hombre fue hallado sin vida por impacto de arma de fuego y maniatado con cinta adhesiva, así como una toalla que cubre la extremidad cefálica.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Se incrementaron los recorridos de seguridad y vigilancia en conjunto con la Policia Municipal, haciendo mayor enfasis en fines de semana y en horario nocturno, con la finalidad de inhibir la comision de homicidios y otros actos delictivos</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ECA26072405507</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-013</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CALZADA DE LA VIGA, Col. JARDINES DE ECATEPEC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>03:30:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Un hombre perdió la vida por impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>* Se establece el acordonamiento del lugar de los hechos.
+* Se establece un perímetro de seguridad. 
+* Se continúa con las entrevistas a los vecinos 
+* No se visualizan cámaras de video vigilancia de domicilios particulares o cercanos a los hechos, no existen cámaras del C5 en la zona.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ECA26072302520</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-014</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CALLE 17 NORTE, Col. LOMAS DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>06:44:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Un hombre de aproximadamente 30 años fue localizado sin vida con impactos de arma de fuego enla extrenidad cefálica, en una bolda de plástico.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Arriba Policía Aguilar Martínez Marcos Jair, con 4 elementos más, para apoyo al Primer Respondiente, al realizar el acordonamiento de seguridad perimetral y preservación del lugar, para continuar con la entrevista y recabar más información. </t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ECA26072302222</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-015</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TECAMAC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>C MAGNOLIAS ESQUINA AV DE LAS ROSAS, Col. LOS HÉROES TECÁMAC III</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Un hombre de aproximadamente 30 años perdió la vida por impactos de arma de fuego en extremidad cefálica y otro más resulto lesionado cuando se encontravan en la tienda con razón social "Abarrotes Las Flores" en el lugar fueron localizados 10 casquillos calibre .40mm y un arma de fuego. El lesionado fue trasladado al Hospital Regional de Tecámac para su atención.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>* Se establece el acordonamiento del lugar de los hechos.
+* Se establece un perímetro de seguridad. 
+* Se continúa con las entrevistas a los vecinos.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ECA26072300766</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-016</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CAMINO NUEVO A HUIXQUILUCAN ESQUINA CON SIERRA HERMOSA, Col. BENITO JUÁREZ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Moisés Plaza Ruiz (49) fue localizado sin vida con disparo de arma de fuego en extremidad cefálica en el asiento del conductor de una camioneta Mazda placas PCX4655 (sin reporte de robo).</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•En la entrevista con el C. Juan Walito Castañeda, mismo que nos menciona que él venía con su amigo de nombre Moisés Plaza Ruiz y su hijo menor de 12 años de edad, abordo del vehículo de la marca Mazda con placas de circulación PCX-46-55, cuando se les empareja una motocicleta donde venían dos masculinos con casco y le dispararon, únicamente lesionando al conductor. Refiriendo que su amigo ya tenía problemas con unos gaseros, y mencionando que había recibido diversas amenazas anteriores por la disputa de reparto de gas LP en pipas</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TOL26072302869</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-018</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TULTEPEC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>C EZEQUIEL FLORES ESQUINA CON HERMANOS SERDÁN, Col. SANTIAGO TEYAHUALCO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>22:15:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Omar Ponce Rodríguez (40) perdió la vida e Isabel Anaya Fragoso resultó lesionada por disparo de arma de fuego, a bordo de una camioneta, tras una discusión con dos hombres con quienes ingerían bebidas alcohólicas.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•En entrevista con su esposa de nombre Isabel Anaya Fragoso. Se realiza entrevista con la esposa del occiso quien refiere que venían circulando sobre la avenida, momento en que se les acerca una motocicleta con dos sujetos a bordo y es cuando escucha las detonaciones a lo que el conductor pierde el control y se detiene con la banqueta, así mismo refiere que por el miedo, salió corriendo del lugar no visualizando a sus atacantes. 
+•Por datos recabados refieren de una unidad de la policía municipal sin precisar número económico que se encontraba a 100 metros del lugar quién escucha las detonaciones, por lo que se dirige al lugar y visualiza a los atacantes sin darles alcance. Por versiones de familiares, el occiso se encontraba ingiriendo bebidas embriagantes y minutos antes tuvo una discusión con unos sujetos por lo que se agreden verbalmente y el aborda su camioneta; los mismos sujetos le dan alcance realizándole las detonaciones huyendo con rumbo desconocido</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>SIN REGISTRO PREVIO 911</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-019</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ACOLMAN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>C PRIMAVERA ESQUINA CON ORQUIDEA, Col. TEPEXPAN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01:50:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Miguel Ángel Rocha Ramírez (20) fue localizado sin vida con impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>* Se apoya con el acordonamiento del lugar de los hechos.
+* Se establece un perímetro de seguridad en el lugar.
+* Se realiza inspección para ubicar cámaras de video vigilancia ya que alrededor del lugar de los hechos no se cuenta con cámaras de vídeo vigilancia en el lugar de los hechos.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ECA26072302393</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-020</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VALLE DE CHALCO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CARRETERA TLÁHUAC-CHALCO, Col. SAN MIGUEL XICO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>19:50:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dos hombres perdieron la vida por disparos de arma de fuego, viajaban en una motocicleta Italika WS150 color azul, placas 71KJZ9 (sin registro)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>• Se apoya con el acordonamiento del lugar de los hechos.
+• Se realiza inspección para ubicar cámaras de video vigilancia.
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ECA26072402231</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-022</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OTZOLOTEPEC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>C DE LA Y ESQUINA AV TOLUCA, Col. GUADALUPE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>21:10:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Un hombre perdió la vida y dos más reusltaron lesionados por impactos de arma de fuego al interior de un estacionamiento de maquinitas.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+• Se apoya con el acordonamiento del lugar de los hechos.
+• Se establece un perímetro de seguridad en el lugar.
+• Se realiza inspección para ubicar cámaras de video vigilancia.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>TOL26072500201</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-023</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AV DE LOS ARCOS ESQUINA CON MIRLO, Col. LA RIVERA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>02:30:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Una persona perdió la vida y tres resultaron lesionadas por impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Al entrevistar a una vecina del lugar, la cual no proporciona generales, misma que refiere que las personas lesionadas estaban ingiriendo bebidas embriagantes en la vía pública desde temprana hora, cuando de repente escucha que empiezan a discutir y se oyen detonaciones de arma de fuego y al salir a checar qué acontecía, visualiza a 01 persona al suelo y tres más lesionadas, y a un vehículo y motocicleta retirarse del sitio con rumbo a la calle El Zapote sin ver placas de los vehículos</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>TOL26072301894</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-024</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TULTEPEC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CALLE TLAXCALA , Col. OXTOC</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>23:10:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Un hombre fue localizado sin vida envuelto con una bolsa plástica de color negro y cinta, sobre un terreno baldio, en los límites con Melchor Ocampo</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ECA26072402446</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-025</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TEOTIHUACAN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CALLE DE LA LUZ, Col. SANTIAGO ATLATONGO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>00:07:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un hombre de aproximadamente 25 años perdió la vida por impactos de arma de fuego </t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Incrementación de recorridos en el área, en coordinación con la Policía Municipal</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ECA26072600093</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-026</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CHICOLOAPAN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CALLE VENEGAS, Col. EMILIANO ZAPATA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01:!0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sergio Manuel Canto Arrieta (51) perdió la vida por impactos de arma de fuego en abdomen y extremidad cefalica al interior de un domicilio.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Se da seguimiento con la Dirección de Unidad de Inteligencia e Investigación para la Prevención y con la Fiscalia Especializada de Homicidios de Alto Impacto del estado de México para la detención de los responsables del homicidio.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ECA26072401839</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-027</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TULTITLAN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AV ISLA COZUMEL, Col. VILLA ESMERALDA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>23:15:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Un hombre de aproximadamente 50 años perdió la vida por impactos de arma de fuego en toráx y extremidad cefálica, en el lugar se localizaron cinco casquillos calibre .9mm.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ECA26072401558</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-028</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CALLE IGNACIO LOPEZ RAYON LT. 10 ESQ INDEPENDENCIA, Col. MIGUEL HIDALGO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>00:01:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>César Cerón Totales (28) y la menor Yoali Giselle Cerón Sánchez (05) perdieron la vida por impactos de arma de fuego a bordo de un vehículo Dodge Charger placas PTK82D.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>• Se entrevista a la C. Gabriela Cerón Torales, Hermana de quien manifiesta que el hoy occiso en vida respondía al nombre de Cesar Cerón Torales de 30 años y la menor de edad de iniciales Y.G.C.S. de 4 años de edad, la cual refiere que había acudido a casa de su expareja del cual está separado y que su hermano se dedica a vender droga.
+• Arriba la unidad médica de Protección Civil y bomberos 627 a mando de Bania Gutiérrez Perales con 1 más a bordo, confirmando el descenso del masculino y la menor.
+• Se establece el acordonamiento del lugar de los hechos.
+• Se establece un perímetro de seguridad.
+• Se continúa con las entrevistas a los vecinos.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ECA26072302222</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-029</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CALLE MIGUEL HIDALGO, Col. LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>00:23:00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Juan Alejandro Cristóbal Reynoso (29) perdio la vida por impactos de arma de fuego a bordo de un vehículo Chevrolet Beat, placas NCJ59A.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>• Se establece el acordonamiento del lugar de los hechos.
+• Se establece un perímetro de seguridad.
+• Se continúa con las entrevistas a los vecinos.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ECA26072301237</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-030</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CHIMALHUACAN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CALLE FRONTERA, Col. ARENITAS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>20:57:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dos hombres fueron localizados sin vida con impactos de arma de fuego, se localizó un cartel con el mensaje: "SIGUE LA LIMPIA PARA TODO AQUEL QUE SIGA SIN ALINEARSE, LA MOLE, NEGRO, TOTOLCO, ALFREDO, JORDAN, QUEMADO, PATO, CHARAL, JAUREGUI, Y TODA LA GENTE DE PANTER Y MARCO ESTEBAN "YOGUR" ABRANSE A LA VERG... JUNTO CON LOS CARRASCO PURO CJNG LIC. VALLARTA ALV !!! (sic)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Se sigue la linea de investigación en coordinación con la fiscala, policia municipal de chimalhuacán asi como con la policía de investigación, para la localización de los responsables</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ECA26072300791</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-031</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AV NORTE 6, Col. SAN ANDRÉS ATENCO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>José Alberto García Montiel (30) perdió la vida por proyectil de arma de fuego en el toráx. El hecho se derivó de un presunto intento de robo de su motocicleta, en el lugar se localizaron 2 casquillos calibre .9mm.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Al entrevistar a la mamá, indica que su hijo no vive en el domicilio donde suscitaron los hechos, que radicaba en la delegación Miguel Hidalgo, Ciudad de México, y hoy vino de visita y que los responsables tripulaban una motocicleta de color roja, uno con casco negro y el otro casco blanco, huyendo con rumbo desconocido. 
+•El dia 20 de julio se llevo a cabo la detencion de 4 personas, se aseguraron 3 motocicletas con reporte de robo y 1 mototocicleta con reporte de robo</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ECA26072409123</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-032</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHIMALHUACAN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>AV ACUITLAPILCO, Col. ACUITLAPILCO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Benjamín "N" "N" de aproximadamente 35 a 40 años perdió la vida por impactos de arma de fuego en el toráx y extremidad inferior izquierda cuando viajaban a bordo de una motocicleta Honda CGL125, de igual manera Armando Posadas García de 43 años resulto lesionado, en el lugar se localizaron 9 casquillos calibre .9mm.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Se sigue la linea de investigación en coordinación con la fiscala, policia municipal de chimalhuacán asi como con la policía de investigación, para la localización de los responsables</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ECA26072507344</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-033</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NEZAHUALCOYOTL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>C ALTAMIRANO 34a, Col. BENITO JUAREZ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>17:47:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Julián Flores Reyes (50) perdió la vida y Luis Rodrigo Romero Luna (25) resultó lesionado por impactos de arma de fuego en el cuello, el lesionado fue trasladado al Hospital Dr. Gustavo Baz Prada, en el lugar se localizaron 7 casquillos calibre .9mm.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Vigilancia perimetral y recorridos para tratar de locailizar el vehiculo y  los responsables</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ECA26072302478</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-034</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>APAXCO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>C FRANCISCO VILLA, Col. LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>20:45:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Raúl Vega Rosales (42) fue localizado por impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>A un costado se aprecia un domicilio particular que cuenta con cámaras dirigidas al lugar de los hechos.
+* Se realiza el acordonamiento del lugar de los hechos, en apoyo y coordinación de la Policía Municipal (primer respondiente).
+* Se establece un perímetro de seguridad.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SIN REGISTRO PREVIO 911</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-035</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ACAMBAY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CARRETERA PANAMERICANA, KM 86, Col. ESDOCA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Mario Alonso Torrijos Pérez (26) falleció por impactos de arma de fuego al exterior de su domicilio</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Se despliega un operatvo en coordinación concon los tres niveles de Gobierno para la búsqueda y localización de los probables responsables.
+en la Mesa de la Construcción por la Paz Se intercambio de información, con la finalidad de disminuir el Delito de Homicidio Doloso.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>TOL26072403529</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-036</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MALINALCO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>C MORELOS, Col. CHALMA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>21:44:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Jaime Esteban Nájera (39) falleció por un impacto de arma de fuego en la cabeza y Antonio Núñez Contreras (22) resultó lesionado, durante una agresión registrada en el compo de fútbol "Los Guayabos".</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Se robustece las acciones operativas en zonas limitrofescon el estado de Morelos, con la finalidad de inhibir el delito de Homicios.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>TOL26072408818</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-037</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CUAUTITLAN IZCALLI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AV TEOLOYUCAN ESQ AV JUAREZ, Col. SAN SEBATIAN XHALA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>22:47:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>César José (34) perdió la vida por impactos de arma de fuego durante un presunto intento de robo de una camioneta Chevrolet Groove, color gris, con placas PAT832A  registrada a nombre de Gabriela Verde Alonso (41) Tras la agresión la camioneta involucrada impactó una unidad de transporte púbico.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•El cuerpo del occiso se encuentra sentado en asiento del conductor, no se aprecian casquillos percutidos en el lugar. En entrevistas informales con los vecinos, refieren que escucharon un ruido y observaron que el vehículo perdía el control y se impactó de frente con una camioneta del servicio público de pasajeros de la ruta unión de concesionarios de Tepotzotlán, con placas de circulación A-04734-E, con el económico 214, la cual circulaba sobre la vialidad, no registrándose más personas lesionadas</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ECA26072600724</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-038</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NICOLAS ROMERO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AV DE LAS TORRES, Col. LIBERTAD</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pablo Muñoz Mercado (50) fue hallado sin vida por impacto de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•En entrevista con vecinos del lugar refieren que el hoy occiso era conocido por dedicarse a la venta de sustancias ilícitas y se le veía en compañía de personas adictas al consumo de las mismas, por las madrugadas en el lugar. Se observa un indicio balístico ( casquillo percutido cal. 9 mm) tirado en el piso. El occiso portaba un accesorio tipo mariconera cerrada, de la cual se desconoce su contenido, en espera del arribo de la autoridad competente, para su revisión.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ECA26072700258</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-039</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA PAZ </t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/D, Col. S/D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>S/D</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Se da seguimiento con la Dirección de Unidad de Inteligencia e Investigación para la Prevención y con la Fiscalia Especializada de Homicidios de Alto Impacto del estado de México para la detención de los responsables del homicidio.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>SIN REGISTRO PREVIO 911</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-040</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ZUMPANGO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>C CANGREJO 2 Y PASEO DEL MAR, Col. FRACCIONAMIENTO SANTA CECILIA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>08:40:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Una mujer de aproximadamente 25 años fue localizada sin vida, con un disparo de arma de fuego en extremidad cefálica en un camino de terracería en la intersección de las calles cangrejo 2 y paseo del mar.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>• Se establece el acordonamiento del lugar de los hechos.
+• Se establece un perímetro de seguridad.
+• Se continúa con las entrevistas a los vecinos.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ECA26072301562</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-041</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CUAUTITLAN IZCALLI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>C BOSQUES AUSTRIACOS ESQ BOSQUES CANADIENSE, Col. BOSQUES DE LA HACIENDA 1RA SECCIÓN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>00:15:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Diego González Terán perdió la vida por disparo de arma de fuego en la nuca y espalda.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+• Por entrevista con los vecinos del lugar manifiestan que escucharon varias detonaciones y al salir ya lo encontraron tirado sin percatarse quien lo lesionó, refieren que el occiso era una persona conflictiva</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ECA26072302610</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-042</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>C COLINAS SAN LORENZO ESQ CATARINAS, Col. LOMA COLORADA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>04:30:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Un hombre (a) "El Jordan" fue hallado sin vida por impactos de arma de fuego, en el lugar se localizaron cuatro casquillos calibre 9mm.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Cabe mencionar que no se encuentran personas en el lugar que pudieran dar información</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>TOL26072508824</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-043</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AV CENTRAL, Col. COLINAS DE SAN MATEO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Rodrigo Jesús Campos López (31) falleció por un impacto de arma de fuego al interior de una unidad de transporte público de la ruta 01, placas 747121J cuando circulaba.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Al entrevistarnos con el hermano C. Raul Campos Lopez,  del  occiso,  manifiesta desconocer algún tipo de amenaza, ya que él únicamente se dedicaba a la práctica de la religión denominada santería.
+•Se entrevista al C. Marco Agusto Ortiz Ávila de 38 años conductor de transporte público, manifiesta que solo escucha que se rompe el vidrio trasero de su microbús y en seguida visualiza como uno de sus pasajeros que venía sentado en el asiento trasero cae al piso. No percatándose de los agresores (infiriendo que no fue ataque directo, si no una bala perdida) por lo cual se orilla sobre la misma vialidad y observa al masculino lesionado, mencionando que no se trató de un asalto.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>TOL26072302178</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-044</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TENANGO DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CAMINO VIEJO A JAJALPA ESQ C LA HACIENDA PONIENTE, Col. SANTA MARÍA JAJALPA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Dos hombres fueron localizados sin vida por disparos de arma de fuego y parcialmente calcinados, en el lugar se localizó una cartulina con mensaje intimidatorio dirigido a "Gael" firmado por el CJNG</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Se establecen canales de comunicación con autoridades de la FGJ, para que mediante cruce de informacion se obtengan datos que permitan dar con los responsables, asi como de las actividades ilicitas a las que se dedican. Incrementando operativos de seguridad interinstitucional, con la finalidad de inhibir el delito.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>TOL26072402922</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-045</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CHIMALHUACAN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>C LLANO VERDE ESQ FRANCISCO JAVIER MINA, Col. XALTIPAC</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>20:11:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Diego Alejandro Salto Martínez (25) perdió la vida por disparo de arma de fuego en extremidad cefálica y toráx, al interior de un vehículo Renault Clio con placas MPN506A, sin reporte de robo, propiedad de José Salto Orozco.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Se sigue la linea de investigación en coordinación con la fiscala, policia municipal de chimalhuacán asi como con la policía de investigación, para la localización de los responsables</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ECA26072304181</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-046</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CUAUTITLAN IZCALLI</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>C RIO CHIQUITO, Col. SAN MATEO IXTACALCO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01:58:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Un hombre fue localizado sin vida por impactos de arma de fuego.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Se entrevista con vecinos mencionando que no escucharon nada, en el lugar se aprecian 15 casquillos calibre 9 milímetros</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ECA26072505152</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-047</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>COYOTEPEC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>C DOMINGO CASTRO ESQ C MIGUEL HIDALGO, Col. LA CABECERA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Joshua Misael Luna Molina (31) perdió la vida por disparo de arma de fuego en un café internet, derivado de una riña con dos personas a quienes agredió con un cuchillo. Fueron localizados 10 casquillos.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Se visualizan heridas por arma de fuego en diferentes partes del cuerpo 
+Se observan cámaras de vigilancia en el exterior del local. 
+Se realiza el acordonamiento del lugar de los hechos, en apoyo y coordinación de la Policía Municipal (primer respondiente).
+Se establece un perímetro de seguridad.
+En el lugar de los hechos solo se localizó un casquillo al parecer 9 mm.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ECA26072209151</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-048</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>VALLE DE BRAVO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>C LOTO AZUL ESQ AV TOLUCA, Col. BARRIO DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Alejandro Ávila Osorio (44) fue localizado sin vida por disparos de arma de fuego en la espalda, en el lugar se hallaron 3 casquillos calibre .223.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Se Implementan filtros de revisión y patrullaje, basándose en la geografía del Barrio de Otumba y las salidas del municipio de Valle de Bravo
+se rediseñan las rutas de patrullaje preventivo de la Policia Estatal en el Barrio de Otumba y zonas aledañas, incrementando la presencia policial a pie-tierra y vehicular en horarios de mayor vulnerabilidad.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>TOL26072300617</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-049</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NICOLAS ROMERO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>C LÁZARO CÁRDENAS ESQ CAMINO A LA PRESA, Col. SAN ISIDRO LA PAZ</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luis Fernando Toledo Trejo (36) (a) “El Zona”, perdió la vida por impactos de arma de fuego sobre calle Lázaro Cárdenas esquina camino a la Presa, colonia San Isidro La Paz, los responsables huyeron a bordo de una motocicleta con rumbo desconocido, en el lugar se localizaron envoltorios con aparente droga y casquillos. </t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Se entrevista con los  vecinos del lugar refieren que el occiso se dedicaba a la venta y distribución de sustancias ilícitas en su domicilio, (taller de reparación de motocicletas) mismo que ya había sido cateado y asegurado por las autoridades de la FGJEM en dos ocasiones diferentes, la primera hace 04 años y la segunda hace un año aproximadamente. El dia de hoy se encontraba en la entrada  de su domicilio, que llegó una motocicleta negra, marca Italika 150, con dos masculinos a bordó y que sin mediar palabra le realizaron varios disparos, al parecer por la disputa del territorio. Se visualizan 14 indicios balísticos percutidos calibre 9 mm.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ECA26072606178</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-050</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>AV 1° MAYO ESQ C EMILIANO ZAPATA, Col. AMPLIACIÓN SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un hombre fue localizado sin vida, con una lesión por proyectil de arma de fuego en la cabeza, en un canal de aguas negras ubicado en la Av. 1º de Mayo esquina con calle Emiliano Zapata, colonia ampliación San Esteban. </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>TOL26072402979</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-051</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CUAUTITLAN IZCALLI</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>C ESCALERAS, Col. SANTA MARÍA DE GUADALUPE, LA QUEBRADA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>02:30:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Leticia Mandujano Romero (42), Oliver Caballero Mandujano (21) y Luis Ángel Caballero Mandujano (17) fueron localizados sin vida por disparos de arma de fuego al interior de un inmueble ubicado sobre la calle Escaleras, colonia Santa María de Guadalupe La Quebrada; en tanto, Jaqueline Caballero Mandujano, con semanas de gestación, resultó lesionada por la misma causa, fue trasladada a un nosocomio</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+•Mediante entrevistas informales con vecinos de la zona refieren que las personas hoy occisas y la lesionada, se dedicaban a la venta de droga, y mencionando que en las noches siempre entraban y salían varias personas sin proporcionar más datos por miedo a represalias. 
+•En seguimiento al a investigacion a los hechos suscitados el 25 Julio del 2026 en la Colonia Santa María Guadalupe Colonia, La Quebrada, Municipio de Cuautitlán Izcalli, en donde fallecieron 3 integrantes de una familia y resultando lesionada la C. Lesli Jiménez Pérez, pareja sentimental de uno de los occisos (Oliver Caballero Mandujano), la cual continúa internada en el Hospital de Traumatologia Lomas Verdes Municipio de Naucalpan México en estado grave con pronóstico reservado por impactos de arma de fuego; Se obtuvo información que los presuntos actos fueron a consecuencia de un ajuste de cuenta entre grupos delictivos relacionado con la venta de drogas (narcomenudeo), ya que según el C. Joan Uriel Caballero Mandujano (familiar de los occisos, vive en un domicilio diferente al de los hechos) las personas que irrumpieron en la casa manifestaron pertenecer a la Fiscalía del Estado y portaban armas Largas y Cortas, mismos en un inicio dirigieron el ataque en contra de su hermano Oliver (occiso) el cual se dedicaba al narcomenudeo, cabe señalar que en estos actos resultó ilesa una hermana de los occisos la cual no a querido proporcionar su identidad ni información a las autoridades y solo a su hermano Joan.
+En el concepto que en citada colonia se mantiene una pugna por acaparar citada actividad ilícita, entre el grupo delictivo “Los Peluches” encabezado por Carlos Ortega, Alias “El Peluchin” y “El Cartel Nuevo Imperio” (Células remanentes del Cartel de Sinaloa) encabezado por Néstor Arturo López Arellano Alias “El 20”.
+El primero respaldado por el Cartel de Caborca y el segundo por la Unión Tepito. </t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ECA26072301288</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-052</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CTO. FUENTES ESQ LAGO ATITLÁN, Col. FUENTES DE ECATEPEC I</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>00:10:00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristián Israel Hernández Huerta (39) murió por disparos de arma de fuego y Blanca Balderas Castañeda (35) resultó lesionada por la misma causa en Cto. Fuentes esquina con Lago Atitlán, colonia Fuentes de Ecatepec I, fue trasladada al Hospital José María Rodríguez. Vecinos indicaron que las víctimas ya habían sido amenazadas; además de que el occiso laboraba para el Lic. Silvano, ex trabajador de la Fiscalía, dedicado a la distribución y venta de droga en la zona. </t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>En el lugar el Policía Garduño Remigio Felipe de Jesús, con 4 elementos más, para apoyo al Primer Respondiente al realizar el acordonamiento de seguridad perimetral y preservación del lugar, para continuar con la entrevista para recabar más información. 
+Se realiza un despliegue con el personal de la fuerza de tarea SEDENA, Guardia Nacional y Policía Estatal que conforman la célula operativa de la estrategia zona oriente a fin de dar con los probables responsables.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ECA26072302520</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-053</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AV DARÍO LÓPEZ ESQ HOUSTON, Col. GRANJAS VALLE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>00:20:00</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Un hombre de aproximadamente 60 años, perdió la vida por impactos de arma de fuego cuando circulaba a bordo de una camioneta Kia con placas PVE902C, sobre Av. Darío López esquina Houston, colonia Granjas Valle, trabajadores de una gasolinera refirieron que dos hombres a bordo de una motocicleta intentaron robarle la camioneta al occiso, quien se impactó contra un árbol provocando la volcadura</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Se han estado realizando patrullajes dinàmicos en las calles aledañas con la instalaciòn de filtros de revisiòn vehìcular y teniendo mayor atenciòn en motocicletas con dos tripulantes con la implementaciòn del Operativo Contra robo a vehìculos, ademàs se realizando reuniones vecinales para informar y restaurar la percepciòn de seguridad en toda el àrea de responsabilidad.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ECA26072301237</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-054</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CUAUTITLAN IZCALLI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>C NOPALTEPEC ESQ AV HUEHUETOCA, Col. COFRADÍA DE SAN MIGUEL I</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>15:44:00</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Marco Antonio Valencia Martínez (52) fue localizado sin vida, con una lesión por proyectil de arma de fuego, en la calle Nopaltepec esquina con Av. Huehuetoca, colonia Cofradía de San Miguel I. 
+De acuerdo con testigos en el lugar, los presuntos responsables escaparon a bordo de una motocicleta con rumbo desconocido</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>•Hasta el momento NO hay detenidos
+• Se despliega un operatvo en coordinación con la Policía Municipal de la localidad para la búsqueda y localización de los probables responsables.
+•Se hizo un recorrido en la zona para detectar camaras vecinales y obtener videos.
+• Se realizan entrevistas informales con transeúntes refieren que el masculino se encontraba en el lugar que se dedicaba a lavar carros, cuando una motocicleta con al parecer dos masculinos lo agredieron, huyendo del lugar.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ECA26072304647</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-055</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EXCEL_CORROBORADOS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TECAMAC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SSEM DGSPYT</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C 5 DE MAYO ESQ C GALEANA, Col. SAN PEDRO ATZOMPA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>00:10:00</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Un hombre de aproximadamente 25 años fue localizado sin vida, con impactos de arma de fuego en la espalda, al exterior de un domicilio ubicado en una privada de la calle 5 de Mayo, esquina con calle Galeana, colonia San Pedro Atzompa, De acuerdo con vecinos de la zona, el occiso no era habitante del lugar.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se  han implementado más recorridos en la zona, así como operativos con las tres instancias de Gobierno, trabajando la proximidad y contacto con la ciudadanía, así como con integrantes de los COPACI, con la finalidad de obtener mayor información de las personas o grupos generadores de violencia en la zona; y asi poder inhibir y  combatir el delito </t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ECA26072303821</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-056</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>INFORME_DOCX</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CÓMPUTO Y CALIDAD</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>C5 / SSEM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ver narrativa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No especificada</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CENTRO DE CONTROL, COMANDO, COMUNICACIÓN, CÓMPUTO Y CALIDAD (C5)
+CENTRO DE ATENCIÓN DE LLAMADAS DE EMERGENCIA 9-1-1  ·  C.A.LL.E.
+INFORME PORMENORIZADO DE INCIDENTES 911
+Enfoque: violencia social percibida, modus operandi, actores, bandas y autoridades coludidas
+Segmentos CSV — 21 y 22 de julio de 2026  |  Folios únicos: 394  |  Prioritarios de alta violencia: 188
+1. Resumen ejecutivo
+Se consolida</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Atención C5</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>SIN REGISTRO PREVIO 911</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-057</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>INFORME_DOCX</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DESCONOCIDO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>C5 / SSEM</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ver narrativa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>No especificada</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PE (Policía Estatal / despacho) concentra la mitad de los cierres capturados; FGJEM aparece en predenuncias de robo de vehículo; CMM (Centros de Mando Municipales) en Toluca y varios municipios; CRUM en lesionados de gravedad. «LIBERADO»/«CANCELADO» suman una proporción relevante de folios sin consolidar en corporación final en el campo.
+9. Geografía de la violencia prioritaria
+Sobre el subconjunt</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Atención C5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>TOL26072301720</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-058</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WHATSAPP_JEFE_MIGUEL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ECATEPEC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>RICARDO HERNÁNDEZ MAYA REYNOSA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>33</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>5 casquillos 9mm</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>GUTIERREZ RAMIREZ JUAN CARLOS (ME334A)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>calle Colorines esquina calle Encino, colonia Tierra Blanca</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>A las 10:55 horas, el Policía GUTIERREZ RAMIREZ JUAN CARLOS unidad ME334A, informó que en calle Colorines esquina calle Encino, colonia Tierra Blanca...</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Primer Respondiente Policía Municipal FERMÍN GUZMÁN FERNANDO (sector 3-21). PC-2021 certifica deceso.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ECA26072301237</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>VINCULADA 911 C5</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-059</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WHATSAPP_JEFE_MIGUEL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TECÁMAC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>LUIS EDUARDO RUIZ ROJAS</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="D59" t="n">
         <v>35</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>7 casquillos 9mm</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Municipal NORMA HERNÁNDEZ CASTRO (C-072)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>No especificada</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>whatsapp_tecamac_chevy.png</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MALDONADO SUÁREZ JUAN TRINIDAD (ME937A5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>calle Jardines de La Viña esquina 2da. Cerrada, Héroes Tecámac</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>A las 23:55 horas, el Policía MALDONADO SUÁREZ JUAN TRINIDAD, unidad ME937A5, informó que a las 06:15 horas, en calle Jardines de La Viña... vehículo Chevrolet Chevy Monza blanco taxi placas PUB383E...</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Primer Respondiente NORMA HERNÁNDEZ CASTRO (C-072). Unidad Médica PC-70.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>SIN REGISTRO PREVIO 911</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>TI-MASIVA-060</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:38:42</t>
         </is>
       </c>
     </row>
